--- a/examples/wangetal2018/out/ResultFiles/AC_0.5_b.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_0.5_b.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="316">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>b</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,24 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
-  </si>
-  <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,25 +130,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -141,6 +175,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -177,6 +214,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -189,6 +232,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -198,27 +244,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -231,39 +298,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -279,6 +337,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -330,24 +391,12 @@
     <t>Electric power (kW)</t>
   </si>
   <si>
-    <t>C_0_0</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
-    <t>C_1_0</t>
-  </si>
-  <si>
-    <t>C_1_1</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
-    <t>C_2_0</t>
-  </si>
-  <si>
     <t>CS3</t>
   </si>
   <si>
@@ -402,198 +451,168 @@
     <t>PI01_0</t>
   </si>
   <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
     <t>PI01_1</t>
   </si>
   <si>
-    <t>PI01_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_remaining</t>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01</t>
+  </si>
+  <si>
+    <t>N02</t>
   </si>
   <si>
     <t>PI02_0</t>
   </si>
   <si>
+    <t>N02_0</t>
+  </si>
+  <si>
     <t>PI02</t>
   </si>
   <si>
+    <t>N03</t>
+  </si>
+  <si>
     <t>PI03_0</t>
   </si>
   <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
     <t>PI03</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI04_0_remaining</t>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0</t>
+  </si>
+  <si>
+    <t>N04_0</t>
   </si>
   <si>
     <t>PI04_1</t>
   </si>
   <si>
+    <t>N04_1</t>
+  </si>
+  <si>
     <t>PI04</t>
   </si>
   <si>
-    <t>PI05_0_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>PI05_0_remaining</t>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0</t>
+  </si>
+  <si>
+    <t>N05_0</t>
   </si>
   <si>
     <t>PI05_1</t>
   </si>
   <si>
+    <t>N05_1</t>
+  </si>
+  <si>
     <t>PI05</t>
   </si>
   <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1</t>
   </si>
   <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
-    <t>PI07_0_remaining</t>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>PI07_0</t>
+  </si>
+  <si>
+    <t>N07_0</t>
   </si>
   <si>
     <t>PI07_1</t>
   </si>
   <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1</t>
   </si>
   <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
     <t>PI09_0</t>
   </si>
   <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1</t>
   </si>
   <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -630,9 +649,6 @@
     <t>Total cost ($)</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>Node</t>
   </si>
   <si>
@@ -661,22 +677,313 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(27.046985282253413), '2049': np.float64(27.723159914309747), '2050': np.float64(28.416238912167486), '2051': np.float64(29.126644884971675), '2052': np.float64(29.85481100709596), '2053': np.float64(30.60118128227336), '2054': np.float64(31.366210814330188), '2055': np.float64(32.150366084688436), '2056': np.float64(32.954125236805645), '2057': np.float64(33.77797836772578), '2058': np.float64(34.62242782691893), '2059': np.float64(35.48798852259189), '2060': np.float64(36.37518823565669), '2061': np.float64(37.284567941548104), '2062': np.float64(38.2166821400868), '2063': np.float64(39.17209919358897), '2064': np.float64(40.151401673428694), '2065': np.float64(41.155186715264406), '2066': np.float64(42.18406638314601), '2067': np.float64(43.238668042724655), '2068': np.float64(44.319634743792776), '2069': np.float64(45.42762561238759), '2070': np.float64(46.56331625269728), '2071': np.float64(47.7273991590147), '2072': np.float64(48.92058413799006), '2073': np.float64(50.14359874143982), '2074': np.float64(51.3971887099758), '2075': np.float64(52.68211842772519), '2076': np.float64(53.99917138841832), '2077': np.float64(55.34915067312877), '2078': np.float64(56.732879439956996), '2079': np.float64(58.1512014259559), '2080': np.float64(59.604981461604794), '2081': np.float64(61.095105998144916), '2082': np.float64(62.62248364809852), '2020': np.float64(13.54723404173073), '2021': np.float64(13.885914892773997), '2022': np.float64(14.233062765093345), '2023': np.float64(14.588889334220678), '2024': np.float64(14.953611567576193), '2025': np.float64(15.327451856765595), '2026': np.float64(15.710638153184735), '2027': np.float64(16.103404107014356), '2028': np.float64(16.50598920968971), '2029': np.float64(16.918638939931952), '2030': np.float64(17.341604913430245), '2031': np.float64(17.775145036266004), '2032': np.float64(18.219523662172655), '2033': np.float64(18.675011753726963), '2034': np.float64(19.14188704757014), '2035': np.float64(19.62043422375939), '2036': np.float64(20.110945079353375), '2037': np.float64(20.613718706337206), '2038': np.float64(21.129061673995636), '2039': np.float64(21.65728821584552), '2040': np.float64(22.19872042124166), '2041': np.float64(22.7536884317727), '2042': np.float64(23.322530642567017), '2043': np.float64(23.90559390863119), '2044': np.float64(24.503233756346965), '2045': np.float64(25.11581460025564), '2046': np.float64(25.743709965262028), '2047': np.float64(26.387302714393577)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.009358718089175568</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333336</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -692,7 +999,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -700,32 +1007,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,14 +1328,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1055,28 +1344,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1084,7 +1373,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1092,7 +1381,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1100,15 +1389,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0.5</v>
@@ -1116,7 +1405,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1124,7 +1413,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1132,7 +1421,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1140,7 +1429,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1148,63 +1437,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>28</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1212,39 +1501,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1254,268 +1604,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>36</v>
+      <c r="C1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B2">
-        <v>0.2338466015361861</v>
+        <v>0.2175539604091935</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B4">
-        <v>0.02679288153103254</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B5">
-        <v>0.03166759958247593</v>
+        <v>0.03246996714111288</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B7">
-        <v>0.006543901761413251</v>
+        <v>0.006709705755068984</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B8">
-        <v>0.01551435456050449</v>
+        <v>0.01590744449964305</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>0.01701801172198348</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11">
-        <v>0.1102274059528919</v>
+        <v>0.1267847442846405</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B15">
-        <v>0.003091196694189028</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B16">
-        <v>0.02201607113791239</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>0.0009751785937831068</v>
+        <v>0.002370193587660122</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.01528585543972777</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.00100803797935677</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B20">
-        <v>13.54723404173073</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>13.54723404173073</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
@@ -1523,396 +1873,361 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B26">
-        <v>14731.96533814537</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B27">
-        <v>4292.970315969958</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B28">
-        <v>178.8737631654149</v>
+        <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>4937.820490526782</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>205.7425204386159</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B31">
-        <v>42936226.13641323</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39">
         <v>24.24086700823207</v>
       </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>48.65964928016304</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41">
+        <v>9.370888513855187</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52">
-        <v>3.437294688060416</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>4609.480922582779</v>
-      </c>
-      <c r="E52">
-        <v>11701763.49018096</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>32.85291374302739</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53">
-        <v>3.146061203317199</v>
-      </c>
-      <c r="C53">
-        <v>12.5</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G53">
-        <v>30.06936754706561</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54">
-        <v>2.947404750452124</v>
-      </c>
-      <c r="C54">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" t="s">
+        <v>110</v>
+      </c>
+      <c r="H54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" t="s">
+        <v>119</v>
+      </c>
+      <c r="H60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61">
+        <v>7.269506166670178</v>
+      </c>
+      <c r="C61">
+        <v>12.5</v>
+      </c>
+      <c r="D61">
         <v>0</v>
       </c>
-      <c r="D54">
-        <v>3952.528718451308</v>
-      </c>
-      <c r="E54">
-        <v>10985514.88815084</v>
-      </c>
-      <c r="F54">
+      <c r="E61">
         <v>0</v>
       </c>
-      <c r="G54">
-        <v>28.1706524519817</v>
-      </c>
-      <c r="H54">
+      <c r="F61">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G61">
+        <v>69.48035612936755</v>
+      </c>
+      <c r="H61">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55">
-        <v>2.128103914093165</v>
-      </c>
-      <c r="C55">
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62">
+        <v>8.895763037145731</v>
+      </c>
+      <c r="C62">
+        <v>12.5</v>
+      </c>
+      <c r="D62">
         <v>0</v>
       </c>
-      <c r="D55">
-        <v>2853.829910877217</v>
-      </c>
-      <c r="E55">
-        <v>9953691.026075777</v>
-      </c>
-      <c r="F55">
+      <c r="E62">
         <v>0</v>
       </c>
-      <c r="G55">
-        <v>20.33995355962709</v>
-      </c>
-      <c r="H55">
+      <c r="F62">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G62">
+        <v>85.02376498381371</v>
+      </c>
+      <c r="H62">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56">
-        <v>2.12058878377824</v>
-      </c>
-      <c r="C56">
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63">
+        <v>5.360908904569065</v>
+      </c>
+      <c r="C63">
         <v>12.5</v>
       </c>
-      <c r="D56">
+      <c r="D63">
         <v>0</v>
       </c>
-      <c r="E56">
+      <c r="E63">
         <v>0</v>
       </c>
-      <c r="F56">
+      <c r="F63">
         <v>16916025.69007904</v>
       </c>
-      <c r="G56">
-        <v>20.26812558140298</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57">
-        <v>2.472838426148799</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>3316.125786234062</v>
-      </c>
-      <c r="E57">
-        <v>10295256.73200565</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>23.63485091834005</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58">
-        <v>2.462694696875903</v>
-      </c>
-      <c r="C58">
-        <v>12.5</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G58">
-        <v>23.53789936397009</v>
-      </c>
-      <c r="H58">
+      <c r="G63">
+        <v>51.23839932543466</v>
+      </c>
+      <c r="H63">
         <v>0</v>
       </c>
     </row>
@@ -1923,63 +2238,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>123</v>
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1987,31 +2302,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F2">
-        <v>99.69069604969901</v>
+        <v>99.81217766689751</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K2">
         <v>8.758481331682836</v>
@@ -2026,16 +2341,16 @@
         <v>8700000</v>
       </c>
       <c r="O2">
-        <v>8413873.687126147</v>
+        <v>8416541.412140448</v>
       </c>
       <c r="P2">
-        <v>9.43299004975235</v>
+        <v>9.611706743212663</v>
       </c>
       <c r="Q2">
-        <v>0.01527670795431803</v>
+        <v>0.0156580916070058</v>
       </c>
       <c r="R2">
-        <v>21.64727926182652</v>
+        <v>21.51663645114532</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2043,31 +2358,31 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F3">
-        <v>99.69069888547529</v>
+        <v>99.81217415867698</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K3">
         <v>8.758481331682836</v>
@@ -2079,19 +2394,19 @@
         <v>8.284946666666665</v>
       </c>
       <c r="N3">
-        <v>8413873.687126147</v>
+        <v>8416541.412140448</v>
       </c>
       <c r="O3">
-        <v>8117821.877883612</v>
+        <v>8123470.43866427</v>
       </c>
       <c r="P3">
-        <v>9.440990829601999</v>
+        <v>9.94926778491091</v>
       </c>
       <c r="Q3">
-        <v>0.01530710946425028</v>
+        <v>0.01622989643328289</v>
       </c>
       <c r="R3">
-        <v>22.03312618787135</v>
+        <v>21.89120630138443</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2099,55 +2414,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F4">
-        <v>99.6907008198246</v>
+        <v>99.81217080822549</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K4">
         <v>8.758481331682836</v>
       </c>
       <c r="L4">
-        <v>8.333333333333332</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M4">
-        <v>5.178091666666666</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N4">
-        <v>8117821.877883612</v>
+        <v>8123470.43866427</v>
       </c>
       <c r="O4">
-        <v>7927248.201786697</v>
+        <v>7819710.791276208</v>
       </c>
       <c r="P4">
-        <v>9.446001754725705</v>
+        <v>10.3258771531589</v>
       </c>
       <c r="Q4">
-        <v>0.01532650529641545</v>
+        <v>0.0168680984215245</v>
       </c>
       <c r="R4">
-        <v>22.29307486976328</v>
+        <v>22.30168195214975</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2155,55 +2470,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>99.54344211732494</v>
+        <v>99.81216727898634</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K5">
         <v>8.758481331682836</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M5">
-        <v>3.106855</v>
+        <v>9.320565</v>
       </c>
       <c r="N5">
-        <v>8758481.331682835</v>
+        <v>7819710.791276208</v>
       </c>
       <c r="O5">
-        <v>8653298.634393794</v>
+        <v>7463593.077845423</v>
       </c>
       <c r="P5">
-        <v>9.338096250750766</v>
+        <v>10.80652138400826</v>
       </c>
       <c r="Q5">
-        <v>0.01510917120725238</v>
+        <v>0.01768293735987287</v>
       </c>
       <c r="R5">
-        <v>21.35004496238852</v>
+        <v>22.81482318192652</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2211,31 +2526,31 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F6">
-        <v>99.54344223104995</v>
+        <v>99.81216340161949</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K6">
         <v>8.758481331682836</v>
@@ -2247,75 +2562,75 @@
         <v>9.320565</v>
       </c>
       <c r="N6">
-        <v>8653298.634393794</v>
+        <v>7463593.077845423</v>
       </c>
       <c r="O6">
-        <v>8329907.201703677</v>
+        <v>7090047.690655245</v>
       </c>
       <c r="P6">
-        <v>9.346826590431576</v>
+        <v>11.36254545044337</v>
       </c>
       <c r="Q6">
-        <v>0.015142115325569</v>
+        <v>0.01862607865961541</v>
       </c>
       <c r="R6">
-        <v>21.75449781763275</v>
+        <v>23.39440337116957</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F7">
-        <v>99.5434423939995</v>
+        <v>99.49956851614276</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K7">
         <v>8.758481331682836</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="M7">
-        <v>9.320565</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N7">
-        <v>8329907.201703677</v>
+        <v>8758481.331682835</v>
       </c>
       <c r="O7">
-        <v>7993633.143069969</v>
+        <v>8426999.521518171</v>
       </c>
       <c r="P7">
-        <v>9.355581617210204</v>
+        <v>9.570028930023701</v>
       </c>
       <c r="Q7">
-        <v>0.01517588115919206</v>
+        <v>0.01558944861214323</v>
       </c>
       <c r="R7">
-        <v>22.20148243366665</v>
+        <v>21.50363690194266</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2323,31 +2638,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>99.40820899327626</v>
+        <v>99.4995684392356</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K8">
         <v>8.758481331682836</v>
@@ -2359,19 +2674,19 @@
         <v>9.786593249999999</v>
       </c>
       <c r="N8">
-        <v>8758481.331682835</v>
+        <v>8426999.521518171</v>
       </c>
       <c r="O8">
-        <v>8423689.845105235</v>
+        <v>8082310.14539748</v>
       </c>
       <c r="P8">
-        <v>9.350472831072285</v>
+        <v>9.967344433243115</v>
       </c>
       <c r="Q8">
-        <v>0.01514249562511609</v>
+        <v>0.01626247708913708</v>
       </c>
       <c r="R8">
-        <v>21.63484803462068</v>
+        <v>21.94547705556749</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2379,55 +2694,55 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>99.40820900006825</v>
+        <v>81.84123826351768</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K9">
         <v>8.758481331682836</v>
       </c>
       <c r="L9">
-        <v>15.75</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M9">
-        <v>9.786593249999999</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N9">
-        <v>8423689.845105235</v>
+        <v>8082310.14539748</v>
       </c>
       <c r="O9">
-        <v>8075240.343752847</v>
+        <v>7832223.007348103</v>
       </c>
       <c r="P9">
-        <v>9.359702363978984</v>
+        <v>8.453522167968858</v>
       </c>
       <c r="Q9">
-        <v>0.01517778902322432</v>
+        <v>0.01380866215207798</v>
       </c>
       <c r="R9">
-        <v>22.09041952223826</v>
+        <v>22.28428189760058</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2435,55 +2750,55 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" t="s">
         <v>160</v>
       </c>
-      <c r="D10" t="s">
-        <v>182</v>
-      </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F10">
-        <v>81.74987908492251</v>
+        <v>81.84123821980802</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K10">
         <v>8.758481331682836</v>
       </c>
       <c r="L10">
-        <v>11.83333333333334</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M10">
-        <v>7.35289016666667</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N10">
-        <v>8075240.343752847</v>
+        <v>7832223.007348103</v>
       </c>
       <c r="O10">
-        <v>7890878.744625815</v>
+        <v>7574090.082851612</v>
       </c>
       <c r="P10">
-        <v>7.702813547948274</v>
+        <v>8.734599410700397</v>
       </c>
       <c r="Q10">
-        <v>0.0124998896361287</v>
+        <v>0.01428511707237468</v>
       </c>
       <c r="R10">
-        <v>22.34373756210782</v>
+        <v>22.65172559290958</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2491,55 +2806,55 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
         <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F11">
-        <v>81.62316498985172</v>
+        <v>81.84123818242837</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K11">
         <v>8.758481331682836</v>
       </c>
       <c r="L11">
-        <v>4.333333333333329</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="M11">
-        <v>2.692607666666664</v>
+        <v>10.04549783333334</v>
       </c>
       <c r="N11">
-        <v>8758481.331682835</v>
+        <v>7574090.082851612</v>
       </c>
       <c r="O11">
-        <v>8696839.04869429</v>
+        <v>7307068.317782541</v>
       </c>
       <c r="P11">
-        <v>7.655741046541454</v>
+        <v>9.046273339251984</v>
       </c>
       <c r="Q11">
-        <v>0.01238501067147943</v>
+        <v>0.01481362542737521</v>
       </c>
       <c r="R11">
-        <v>21.29738397672895</v>
+        <v>23.05232049996028</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2547,55 +2862,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
         <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F12">
-        <v>81.62316498992803</v>
+        <v>81.84123815192058</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K12">
         <v>8.758481331682836</v>
       </c>
       <c r="L12">
-        <v>16.16666666666667</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M12">
-        <v>10.04549783333334</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N12">
-        <v>8696839.04869429</v>
+        <v>7307068.317782541</v>
       </c>
       <c r="O12">
-        <v>8462966.932250882</v>
+        <v>7021419.278045881</v>
       </c>
       <c r="P12">
-        <v>7.663453453071625</v>
+        <v>9.405818831281492</v>
       </c>
       <c r="Q12">
-        <v>0.01240859162410618</v>
+        <v>0.01542361474777464</v>
       </c>
       <c r="R12">
-        <v>21.58532078046117</v>
+        <v>23.50596584320128</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2603,55 +2918,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F13">
-        <v>81.62316499006117</v>
+        <v>81.84123813674643</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>8.758481331682836</v>
       </c>
       <c r="L13">
-        <v>16.16666666666667</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M13">
-        <v>10.04549783333334</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N13">
-        <v>8462966.932250882</v>
+        <v>7021419.278045881</v>
       </c>
       <c r="O13">
-        <v>8222545.415538021</v>
+        <v>6723924.212105002</v>
       </c>
       <c r="P13">
-        <v>7.671189351154662</v>
+        <v>9.812611582964902</v>
       </c>
       <c r="Q13">
-        <v>0.01243269601203564</v>
+        <v>0.01611413019705806</v>
       </c>
       <c r="R13">
-        <v>21.89409575857635</v>
+        <v>24.00889101705258</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2659,143 +2974,143 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F14">
-        <v>81.6231649901295</v>
+        <v>81.84123813442251</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K14">
         <v>8.758481331682836</v>
       </c>
       <c r="L14">
-        <v>6.666666666666671</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M14">
-        <v>4.142473333333336</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N14">
-        <v>8222545.415538021</v>
+        <v>6723924.212105002</v>
       </c>
       <c r="O14">
-        <v>8121358.479458209</v>
+        <v>6412953.693113433</v>
       </c>
       <c r="P14">
-        <v>7.674386281225481</v>
+        <v>10.27798540680215</v>
       </c>
       <c r="Q14">
-        <v>0.01244266462466221</v>
+        <v>0.01690454558394771</v>
       </c>
       <c r="R14">
-        <v>22.02838772572116</v>
+        <v>24.5716202324457</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F15">
-        <v>81.53167367628195</v>
+        <v>81.45879314629151</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K15">
         <v>8.758481331682836</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M15">
-        <v>6.21371</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N15">
         <v>8758481.331682835</v>
       </c>
       <c r="O15">
-        <v>8615891.687573487</v>
+        <v>8522708.328748496</v>
       </c>
       <c r="P15">
-        <v>7.657967495026451</v>
+        <v>7.74917241120858</v>
       </c>
       <c r="Q15">
-        <v>0.0123924555541371</v>
+        <v>0.01261778717283178</v>
       </c>
       <c r="R15">
-        <v>21.39567764541531</v>
+        <v>21.3857540391465</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F16">
-        <v>81.53167367628342</v>
+        <v>81.45879314455158</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K16">
         <v>8.758481331682836</v>
@@ -2807,51 +3122,51 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N16">
-        <v>8615891.687573487</v>
+        <v>8522708.328748496</v>
       </c>
       <c r="O16">
-        <v>8372928.667971016</v>
+        <v>8280408.623281932</v>
       </c>
       <c r="P16">
-        <v>7.665943845425256</v>
+        <v>7.969781872463122</v>
       </c>
       <c r="Q16">
-        <v>0.01241695495143987</v>
+        <v>0.01299144307375966</v>
       </c>
       <c r="R16">
-        <v>21.6993643005018</v>
+        <v>21.68803090501151</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F17">
-        <v>81.53167367628583</v>
+        <v>81.45879314177786</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K17">
         <v>8.758481331682836</v>
@@ -2863,19 +3178,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N17">
-        <v>8372928.667971016</v>
+        <v>8280408.623281932</v>
       </c>
       <c r="O17">
-        <v>8122810.632938321</v>
+        <v>8030998.815635343</v>
       </c>
       <c r="P17">
-        <v>7.673945317434258</v>
+        <v>8.210929194082707</v>
       </c>
       <c r="Q17">
-        <v>0.01244188062487829</v>
+        <v>0.01339994222662952</v>
       </c>
       <c r="R17">
-        <v>22.02644296500717</v>
+        <v>22.01370079569834</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2883,31 +3198,31 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F18">
-        <v>81.44050544115737</v>
+        <v>81.45879313670625</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K18">
         <v>8.758481331682836</v>
@@ -2919,19 +3234,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N18">
-        <v>8758481.331682835</v>
+        <v>8030998.815635343</v>
       </c>
       <c r="O18">
-        <v>8520056.163540566</v>
+        <v>7773800.19007257</v>
       </c>
       <c r="P18">
-        <v>7.66216432762607</v>
+        <v>8.475749267657525</v>
       </c>
       <c r="Q18">
-        <v>0.01240378118349813</v>
+        <v>0.01384873831561645</v>
       </c>
       <c r="R18">
-        <v>21.51393562871387</v>
+        <v>22.36587823879457</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2939,31 +3254,31 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F19">
-        <v>81.44050544115737</v>
+        <v>81.45879312345953</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K19">
         <v>8.758481331682836</v>
@@ -2975,19 +3290,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N19">
-        <v>8520056.163540566</v>
+        <v>7773800.19007257</v>
       </c>
       <c r="O19">
-        <v>8274866.56989496</v>
+        <v>7508014.388382703</v>
       </c>
       <c r="P19">
-        <v>7.670171971991958</v>
+        <v>8.768417046254553</v>
       </c>
       <c r="Q19">
-        <v>0.01242857107763413</v>
+        <v>0.01434494224408147</v>
       </c>
       <c r="R19">
-        <v>21.82565094000351</v>
+        <v>22.74874825689941</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2995,31 +3310,31 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F20">
-        <v>81.44050544115736</v>
+        <v>81.45879304051512</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K20">
         <v>8.758481331682836</v>
@@ -3031,107 +3346,107 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N20">
-        <v>8274866.56989496</v>
+        <v>7508014.388382703</v>
       </c>
       <c r="O20">
-        <v>8022291.781275438</v>
+        <v>7232705.25373624</v>
       </c>
       <c r="P20">
-        <v>7.678204922037245</v>
+        <v>9.094422286699121</v>
       </c>
       <c r="Q20">
-        <v>0.01245359411427494</v>
+        <v>0.01489779342601277</v>
       </c>
       <c r="R20">
-        <v>22.16228900169007</v>
+        <v>23.16778233123985</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" t="s">
         <v>143</v>
       </c>
-      <c r="C21" t="s">
-        <v>171</v>
-      </c>
-      <c r="D21" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" t="s">
-        <v>188</v>
-      </c>
       <c r="F21">
-        <v>81.33419330879887</v>
+        <v>81.22831727498141</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K21">
         <v>8.758481331682836</v>
       </c>
       <c r="L21">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M21">
-        <v>10.35618333333333</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N21">
         <v>8758481.331682835</v>
       </c>
       <c r="O21">
-        <v>8520672.888320364</v>
+        <v>8524028.676187318</v>
       </c>
       <c r="P21">
-        <v>7.652162166862091</v>
+        <v>7.726081856033258</v>
       </c>
       <c r="Q21">
-        <v>0.01238756004551987</v>
+        <v>0.01258011391665273</v>
       </c>
       <c r="R21">
-        <v>21.51316832996786</v>
+        <v>21.38414132095695</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>81.33419330879902</v>
+        <v>81.22831727338904</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K22">
         <v>8.758481331682836</v>
@@ -3143,51 +3458,51 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N22">
-        <v>8520672.888320364</v>
+        <v>8524028.676187318</v>
       </c>
       <c r="O22">
-        <v>8276135.970718376</v>
+        <v>8283124.304955893</v>
       </c>
       <c r="P22">
-        <v>7.660159358078846</v>
+        <v>7.944697561487946</v>
       </c>
       <c r="Q22">
-        <v>0.0124122849081201</v>
+        <v>0.01295039032122468</v>
       </c>
       <c r="R22">
-        <v>21.82400206435616</v>
+        <v>21.6845716625815</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F23">
-        <v>81.33419330879883</v>
+        <v>81.22831727243627</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K23">
         <v>8.758481331682836</v>
@@ -3199,19 +3514,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N23">
-        <v>8276135.970718376</v>
+        <v>8283124.304955893</v>
       </c>
       <c r="O23">
-        <v>8024254.988646143</v>
+        <v>8035195.245405112</v>
       </c>
       <c r="P23">
-        <v>7.668181821941056</v>
+        <v>8.183529800907341</v>
       </c>
       <c r="Q23">
-        <v>0.01243724298932732</v>
+        <v>0.01335496685139867</v>
       </c>
       <c r="R23">
-        <v>22.15961171827651</v>
+        <v>22.00809730132054</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3219,31 +3534,31 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F24">
-        <v>81.22831727508496</v>
+        <v>81.22831727927995</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K24">
         <v>8.758481331682836</v>
@@ -3255,19 +3570,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N24">
-        <v>8758481.331682835</v>
+        <v>8035195.245405112</v>
       </c>
       <c r="O24">
-        <v>8521286.26191951</v>
+        <v>7779575.092739929</v>
       </c>
       <c r="P24">
-        <v>7.642201035551829</v>
+        <v>8.445643570706499</v>
       </c>
       <c r="Q24">
-        <v>0.01237140556456692</v>
+        <v>0.01379917577604244</v>
       </c>
       <c r="R24">
-        <v>21.51240528202044</v>
+        <v>22.35777276478256</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -3275,31 +3590,31 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F25">
-        <v>81.22831727508526</v>
+        <v>81.22831727763095</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K25">
         <v>8.758481331682836</v>
@@ -3311,19 +3626,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N25">
-        <v>8521286.26191951</v>
+        <v>7779575.092739929</v>
       </c>
       <c r="O25">
-        <v>8277398.373414061</v>
+        <v>7515481.405987513</v>
       </c>
       <c r="P25">
-        <v>7.650187816498916</v>
+        <v>8.735128806345539</v>
       </c>
       <c r="Q25">
-        <v>0.0123960658021778</v>
+        <v>0.01428997563324119</v>
       </c>
       <c r="R25">
-        <v>21.82236264942306</v>
+        <v>22.73771507243059</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -3331,31 +3646,31 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D26" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F26">
-        <v>81.22831727508522</v>
+        <v>81.22831727417801</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K26">
         <v>8.758481331682836</v>
@@ -3367,187 +3682,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>8277398.373414061</v>
+        <v>7515481.405987513</v>
       </c>
       <c r="O26">
-        <v>8026207.197351886</v>
+        <v>7241997.545758328</v>
       </c>
       <c r="P26">
-        <v>7.658199837193025</v>
+        <v>9.057325000459917</v>
       </c>
       <c r="Q26">
-        <v>0.01242095934285899</v>
+        <v>0.01483635897527038</v>
       </c>
       <c r="R26">
-        <v>22.15695039597083</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" t="s">
-        <v>178</v>
-      </c>
-      <c r="E27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27">
-        <v>81.22831727508513</v>
-      </c>
-      <c r="G27">
-        <v>650</v>
-      </c>
-      <c r="H27" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27">
-        <v>9.525</v>
-      </c>
-      <c r="J27" t="s">
-        <v>84</v>
-      </c>
-      <c r="K27">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="L27">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M27">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N27">
-        <v>8026207.197351886</v>
-      </c>
-      <c r="O27">
-        <v>7767001.528345278</v>
-      </c>
-      <c r="P27">
-        <v>7.66623723116434</v>
-      </c>
-      <c r="Q27">
-        <v>0.01244641791198004</v>
-      </c>
-      <c r="R27">
-        <v>22.51926128244549</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28">
-        <v>3</v>
-      </c>
-      <c r="B28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" t="s">
-        <v>188</v>
-      </c>
-      <c r="F28">
-        <v>81.22831727508509</v>
-      </c>
-      <c r="G28">
-        <v>650</v>
-      </c>
-      <c r="H28" t="s">
-        <v>85</v>
-      </c>
-      <c r="I28">
-        <v>9.525</v>
-      </c>
-      <c r="J28" t="s">
-        <v>84</v>
-      </c>
-      <c r="K28">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="L28">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M28">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N28">
-        <v>7767001.528345278</v>
-      </c>
-      <c r="O28">
-        <v>7498940.920282046</v>
-      </c>
-      <c r="P28">
-        <v>7.674300132935468</v>
-      </c>
-      <c r="Q28">
-        <v>0.01247234975703727</v>
-      </c>
-      <c r="R28">
-        <v>22.91398842901298</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F29">
-        <v>81.22831727508516</v>
-      </c>
-      <c r="G29">
-        <v>650</v>
-      </c>
-      <c r="H29" t="s">
-        <v>85</v>
-      </c>
-      <c r="I29">
-        <v>9.525</v>
-      </c>
-      <c r="J29" t="s">
-        <v>84</v>
-      </c>
-      <c r="K29">
-        <v>8.758481331682836</v>
-      </c>
-      <c r="L29">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M29">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N29">
-        <v>7498940.920282046</v>
-      </c>
-      <c r="O29">
-        <v>7221038.466508406</v>
-      </c>
-      <c r="P29">
-        <v>7.682388678030966</v>
-      </c>
-      <c r="Q29">
-        <v>0.01249873002769165</v>
-      </c>
-      <c r="R29">
-        <v>23.34681789871137</v>
+        <v>23.15325949019977</v>
       </c>
     </row>
   </sheetData>
@@ -3557,104 +3704,101 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
         <v>196</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="G1" t="s">
         <v>197</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="H1" t="s">
         <v>198</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="I1" t="s">
         <v>199</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="J1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" t="s">
         <v>200</v>
       </c>
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>205</v>
+      </c>
+      <c r="R1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2">
-        <v>0</v>
-      </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>21.747985</v>
+        <v>43.49597</v>
       </c>
       <c r="H2">
-        <v>1.104857714649175</v>
+        <v>1.235320510358005</v>
       </c>
       <c r="I2">
-        <v>32.85291374302739</v>
+        <v>69.48035612936755</v>
       </c>
       <c r="J2">
-        <v>3.437294688060416</v>
+        <v>7.269506166670178</v>
       </c>
       <c r="K2">
-        <v>4609.480922582779</v>
+        <v>9748.553159628042</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>3.437294688060416</v>
+        <v>12.5</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -3663,45 +3807,45 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>11701763.49018096</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R2">
-        <v>11701763.49018096</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="B3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G3">
-        <v>43.49597</v>
+        <v>124.2742</v>
       </c>
       <c r="H3">
-        <v>1.095682172914821</v>
+        <v>1.36574841341645</v>
       </c>
       <c r="I3">
-        <v>30.06936754706561</v>
+        <v>85.02376498381371</v>
       </c>
       <c r="J3">
-        <v>3.146061203317199</v>
+        <v>8.895763037145731</v>
       </c>
       <c r="K3">
-        <v>4218.93099487243</v>
+        <v>11929.39614807317</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -3726,44 +3870,41 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4">
-        <v>1</v>
-      </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="F4">
-        <v>113.3333333333333</v>
+        <v>300</v>
       </c>
       <c r="G4">
-        <v>70.42204666666667</v>
+        <v>186.4113</v>
       </c>
       <c r="H4">
-        <v>1.109950059446537</v>
+        <v>1.210955102471294</v>
       </c>
       <c r="I4">
-        <v>28.1706524519817</v>
+        <v>51.23839932543466</v>
       </c>
       <c r="J4">
-        <v>2.947404750452124</v>
+        <v>5.360908904569065</v>
       </c>
       <c r="K4">
-        <v>3952.528718451308</v>
+        <v>7189.086059205208</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2.947404750452124</v>
+        <v>12.5</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -3772,230 +3913,12 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>10985514.88815084</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R4">
-        <v>10985514.88815084</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5">
-        <v>156.6666666666667</v>
-      </c>
-      <c r="G5">
-        <v>97.34812333333335</v>
-      </c>
-      <c r="H5">
-        <v>1.078450280681013</v>
-      </c>
-      <c r="I5">
-        <v>20.33995355962709</v>
-      </c>
-      <c r="J5">
-        <v>2.128103914093165</v>
-      </c>
-      <c r="K5">
-        <v>2853.829910877217</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>2.128103914093165</v>
-      </c>
-      <c r="N5">
-        <v>0.78</v>
-      </c>
-      <c r="O5">
-        <v>0.357</v>
-      </c>
-      <c r="P5">
-        <v>9953691.026075777</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>9953691.026075777</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6">
-        <v>200</v>
-      </c>
-      <c r="G6">
-        <v>124.2742</v>
-      </c>
-      <c r="H6">
-        <v>1.078257480996399</v>
-      </c>
-      <c r="I6">
-        <v>20.26812558140298</v>
-      </c>
-      <c r="J6">
-        <v>2.12058878377824</v>
-      </c>
-      <c r="K6">
-        <v>2843.751970822295</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>12.5</v>
-      </c>
-      <c r="N6">
-        <v>0.78</v>
-      </c>
-      <c r="O6">
-        <v>0.357</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R6">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7">
-        <v>250</v>
-      </c>
-      <c r="G7">
-        <v>155.34275</v>
-      </c>
-      <c r="H7">
-        <v>1.091767984820212</v>
-      </c>
-      <c r="I7">
-        <v>23.63485091834005</v>
-      </c>
-      <c r="J7">
-        <v>2.472838426148799</v>
-      </c>
-      <c r="K7">
-        <v>3316.125786234062</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>2.472838426148799</v>
-      </c>
-      <c r="N7">
-        <v>0.78</v>
-      </c>
-      <c r="O7">
-        <v>0.357</v>
-      </c>
-      <c r="P7">
-        <v>10295256.73200565</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>10295256.73200565</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G8">
-        <v>186.4113</v>
-      </c>
-      <c r="H8">
-        <v>1.091500873797702</v>
-      </c>
-      <c r="I8">
-        <v>23.53789936397009</v>
-      </c>
-      <c r="J8">
-        <v>2.462694696875903</v>
-      </c>
-      <c r="K8">
-        <v>3302.522842404523</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>12.5</v>
-      </c>
-      <c r="N8">
-        <v>0.78</v>
-      </c>
-      <c r="O8">
-        <v>0.357</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R8">
         <v>16916025.69007904</v>
       </c>
     </row>
@@ -4006,20 +3929,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>203</v>
+      <c r="A1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B2">
         <v>8700000</v>
@@ -4027,74 +3950,74 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B3">
-        <v>8413873.687126147</v>
+        <v>8416541.412140448</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <v>8117821.877883612</v>
+        <v>8123470.43866427</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="B5">
-        <v>7927248.201786697</v>
+        <v>7819710.791276208</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B6">
-        <v>8758481.331682835</v>
+        <v>7463593.077845423</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B7">
-        <v>8653298.634393794</v>
+        <v>7090047.690655245</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B8">
-        <v>8329907.201703677</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="B9">
-        <v>7993633.143069969</v>
+        <v>8426999.521518171</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B10">
-        <v>8758481.331682835</v>
+        <v>8082310.14539748</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B11">
-        <v>8423689.845105235</v>
+        <v>7832223.007348103</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4102,207 +4025,151 @@
         <v>160</v>
       </c>
       <c r="B12">
-        <v>8075240.343752847</v>
+        <v>7574090.082851612</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="B13">
-        <v>7890878.744625815</v>
+        <v>7307068.317782541</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14">
-        <v>8758481.331682835</v>
+        <v>7021419.278045881</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B15">
-        <v>8696839.04869429</v>
+        <v>6723924.212105002</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B16">
-        <v>8462966.932250882</v>
+        <v>6412953.693113433</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B17">
-        <v>8222545.415538021</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B18">
-        <v>8121358.479458209</v>
+        <v>8522708.328748496</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B19">
-        <v>8758481.331682835</v>
+        <v>8280408.623281932</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B20">
-        <v>8615891.687573487</v>
+        <v>8030998.815635343</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B21">
-        <v>8372928.667971016</v>
+        <v>7773800.19007257</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B22">
-        <v>8122810.632938321</v>
+        <v>7508014.388382703</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B23">
-        <v>8758481.331682835</v>
+        <v>7232705.25373624</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B24">
-        <v>8520056.163540566</v>
+        <v>8758481.331682835</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B25">
-        <v>8274866.56989496</v>
+        <v>8524028.676187318</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B26">
-        <v>8022291.781275438</v>
+        <v>8283124.304955893</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B27">
-        <v>8758481.331682835</v>
+        <v>8035195.245405112</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B28">
-        <v>8520672.888320364</v>
+        <v>7779575.092739929</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B29">
-        <v>8276135.970718376</v>
+        <v>7515481.405987513</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B30">
-        <v>8024254.988646143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>174</v>
-      </c>
-      <c r="B31">
-        <v>8758481.331682835</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B32">
-        <v>8521286.26191951</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B33">
-        <v>8277398.373414061</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34">
-        <v>8026207.197351886</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35">
-        <v>7767001.528345278</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>179</v>
-      </c>
-      <c r="B36">
-        <v>7498940.920282046</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>187</v>
-      </c>
-      <c r="B37">
-        <v>7221038.466508406</v>
+        <v>7241997.545758328</v>
       </c>
     </row>
   </sheetData>
@@ -4316,37 +4183,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="A1" t="s">
         <v>209</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B1" t="s">
         <v>210</v>
+      </c>
+      <c r="C1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B2">
         <v>17.65832997587177</v>
       </c>
       <c r="C2">
-        <v>17.65832991514574</v>
+        <v>17.65833017571792</v>
       </c>
       <c r="D2">
         <v>65.15454188318284</v>
@@ -4355,21 +4222,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520396043424</v>
+        <v>1150.520413020885</v>
       </c>
       <c r="G2">
-        <v>-3.438944872133598E-07</v>
+        <v>1.131738708570636E-06</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B3">
         <v>45.91165732334162</v>
       </c>
       <c r="C3">
-        <v>45.91165732334163</v>
+        <v>45.91165732282889</v>
       </c>
       <c r="D3">
         <v>65.15454188318284</v>
@@ -4378,21 +4245,21 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.353000000001</v>
+        <v>2991.352999966593</v>
       </c>
       <c r="G3">
-        <v>1.547630334396267E-14</v>
+        <v>-1.116770049300346E-09</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B4">
         <v>35.31665995174353</v>
       </c>
       <c r="C4">
-        <v>35.31665995174353</v>
+        <v>35.31665995134912</v>
       </c>
       <c r="D4">
         <v>65.15454188318284</v>
@@ -4401,10 +4268,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.0408</v>
+        <v>2301.040799974302</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-1.116776224888291E-09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" t="s">
+        <v>246</v>
+      </c>
+      <c r="I9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" t="s">
+        <v>263</v>
+      </c>
+      <c r="H20" t="s">
+        <v>264</v>
+      </c>
+      <c r="I20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>269</v>
+      </c>
+      <c r="B23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>283</v>
+      </c>
+      <c r="B32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>286</v>
+      </c>
+      <c r="B34" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B35" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>289</v>
+      </c>
+      <c r="B36" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>291</v>
+      </c>
+      <c r="B37" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F37" t="s">
+        <v>294</v>
+      </c>
+      <c r="G37" t="s">
+        <v>226</v>
+      </c>
+      <c r="H37" t="s">
+        <v>295</v>
+      </c>
+      <c r="I37" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" t="s">
+        <v>293</v>
+      </c>
+      <c r="E38" t="s">
+        <v>261</v>
+      </c>
+      <c r="F38" t="s">
+        <v>294</v>
+      </c>
+      <c r="G38" t="s">
+        <v>226</v>
+      </c>
+      <c r="H38" t="s">
+        <v>295</v>
+      </c>
+      <c r="I38" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" t="s">
+        <v>292</v>
+      </c>
+      <c r="C39" t="s">
+        <v>299</v>
+      </c>
+      <c r="D39" t="s">
+        <v>293</v>
+      </c>
+      <c r="E39" t="s">
+        <v>261</v>
+      </c>
+      <c r="F39" t="s">
+        <v>294</v>
+      </c>
+      <c r="G39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H39" t="s">
+        <v>295</v>
+      </c>
+      <c r="I39" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>300</v>
+      </c>
+      <c r="B40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" t="s">
+        <v>293</v>
+      </c>
+      <c r="E40" t="s">
+        <v>261</v>
+      </c>
+      <c r="F40" t="s">
+        <v>294</v>
+      </c>
+      <c r="G40" t="s">
+        <v>226</v>
+      </c>
+      <c r="H40" t="s">
+        <v>295</v>
+      </c>
+      <c r="I40" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" t="s">
+        <v>292</v>
+      </c>
+      <c r="C41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D41" t="s">
+        <v>293</v>
+      </c>
+      <c r="E41" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41" t="s">
+        <v>295</v>
+      </c>
+      <c r="I41" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>303</v>
+      </c>
+      <c r="B42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" t="s">
+        <v>304</v>
+      </c>
+      <c r="D42" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" t="s">
+        <v>294</v>
+      </c>
+      <c r="G42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42" t="s">
+        <v>295</v>
+      </c>
+      <c r="I42" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>305</v>
+      </c>
+      <c r="B43" t="s">
+        <v>292</v>
+      </c>
+      <c r="C43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" t="s">
+        <v>293</v>
+      </c>
+      <c r="E43" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" t="s">
+        <v>294</v>
+      </c>
+      <c r="G43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H43" t="s">
+        <v>295</v>
+      </c>
+      <c r="I43" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" t="s">
+        <v>261</v>
+      </c>
+      <c r="F44" t="s">
+        <v>294</v>
+      </c>
+      <c r="G44" t="s">
+        <v>226</v>
+      </c>
+      <c r="H44" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" t="s">
+        <v>294</v>
+      </c>
+      <c r="G45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H45" t="s">
+        <v>295</v>
+      </c>
+      <c r="I45" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>307</v>
+      </c>
+      <c r="B46" t="s">
+        <v>292</v>
+      </c>
+      <c r="C46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D46" t="s">
+        <v>309</v>
+      </c>
+      <c r="E46" t="s">
+        <v>310</v>
+      </c>
+      <c r="F46" t="s">
+        <v>242</v>
+      </c>
+      <c r="G46" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>311</v>
+      </c>
+      <c r="B47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" t="s">
+        <v>280</v>
+      </c>
+      <c r="D47" t="s">
+        <v>309</v>
+      </c>
+      <c r="E47" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>312</v>
+      </c>
+      <c r="B48" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" t="s">
+        <v>309</v>
+      </c>
+      <c r="E48" t="s">
+        <v>231</v>
+      </c>
+      <c r="F48" t="s">
+        <v>242</v>
+      </c>
+      <c r="G48" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>313</v>
+      </c>
+      <c r="B49" t="s">
+        <v>292</v>
+      </c>
+      <c r="C49" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" t="s">
+        <v>309</v>
+      </c>
+      <c r="E49" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" t="s">
+        <v>242</v>
+      </c>
+      <c r="G49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>314</v>
+      </c>
+      <c r="B50" t="s">
+        <v>292</v>
+      </c>
+      <c r="C50" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
